--- a/SHOP_Qcut_交易通路.xlsx
+++ b/SHOP_Qcut_交易通路.xlsx
@@ -413,36 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SHAP_Min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SHAP_Max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Feature_Mean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SHAP_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SHAP_Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SHAP_Std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fraud_Prob</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cnt</t>
         </is>
@@ -450,41 +460,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>-1.793599963188171</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5027999877929688</v>
+      </c>
+      <c r="C2" t="n">
         <v>4.8639</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>-0.4478999972343445</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>-0.4068000018596649</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.2644999921321869</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.8600999712944031</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>3203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>-0.048700001090765</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8550000190734863</v>
+      </c>
+      <c r="C3" t="n">
         <v>7</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>0.3621000051498413</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>0.3583999872207642</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.1454000025987625</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.8664000034332275</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>10899</v>
       </c>
     </row>
